--- a/data/trans_dic/P43C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Habitat-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>62,47%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,84%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,43; 51,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,42; 65,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,22; 59,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,1; 56,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,35; 50,67</t>
+          <t>43,43; 51,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,79; 66,37</t>
+          <t>58,42; 65,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,63; 59,55</t>
+          <t>52,22; 59,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,2; 56,49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43,35; 50,67</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58,79; 66,37</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51,63; 59,55</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,2; 56,49</t>
+          <t>49,1; 56,38</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64,61%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>65,15%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>52,29%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,5; 54,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,7; 67,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,25; 68,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,94; 55,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 55,15</t>
+          <t>48,5; 54,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,49; 67,57</t>
+          <t>61,7; 67,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,14; 68,0</t>
+          <t>62,25; 68,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,1; 55,3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48,6; 55,15</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61,49; 67,57</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>62,14; 68,0</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>49,1; 55,3</t>
+          <t>48,94; 55,48</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>56,6%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>48,85%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,53; 60,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,92; 73,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,56; 68,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,14; 70,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,77; 59,98</t>
+          <t>52,53; 60,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,49; 73,57</t>
+          <t>66,92; 73,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,99; 68,26</t>
+          <t>61,56; 68,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,48; 69,49</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>52,77; 59,98</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66,49; 73,57</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>60,99; 68,26</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>21,48; 69,49</t>
+          <t>23,14; 70,15</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67,08%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67,32%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,08%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,31; 61,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,23; 66,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,46; 70,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,57; 74,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,4; 61,1</t>
+          <t>55,31; 61,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,51; 66,47</t>
+          <t>60,23; 66,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,18; 70,42</t>
+          <t>64,46; 70,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 74,48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55,4; 61,1</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60,51; 66,47</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>64,18; 70,42</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>62,75; 74,48</t>
+          <t>62,57; 74,76</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>55,97%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,98; 55,46</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,58; 66,93</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,29; 65,57</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,79; 61,47</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51,98; 55,46</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>63,58; 66,93</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62,29; 65,57</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>43,79; 61,47</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
     </row>
@@ -1344,16 +1108,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1378,22 +1141,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,20 +1160,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1455,26 +1206,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1491,10 +1222,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1509,22 +1236,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1543,26 +1270,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>500</t>
         </is>
@@ -1577,22 +1284,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317649</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431039</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1611,26 +1318,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>267433</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>317649</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>431039</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>370525</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>267433</t>
         </is>
@@ -1645,62 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>292982; 344052</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>403092; 455070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>347554; 396955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>248548; 285365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>292397; 341803</t>
+          <t>292982; 344052</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>405584; 457891</t>
+          <t>403092; 455070</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>343626; 396335</t>
+          <t>347554; 396955</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249040; 285916</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>292397; 341803</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>405584; 457891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>343626; 396335</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>249040; 285916</t>
+          <t>248548; 285365</t>
         </is>
       </c>
     </row>
@@ -1717,22 +1384,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1751,26 +1418,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>643</t>
         </is>
@@ -1785,22 +1432,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495667</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>662081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,26 +1466,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380965</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>495667</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>662081</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>668829</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>380965</t>
         </is>
@@ -1853,62 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>463808; 525577</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>632346; 695696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>639013; 700781</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>356534; 404163</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>464816; 527472</t>
+          <t>463808; 525577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>630143; 692443</t>
+          <t>632346; 695696</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>637955; 698073</t>
+          <t>639013; 700781</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>357717; 402860</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>464816; 527472</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>630143; 692443</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>637955; 698073</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>357717; 402860</t>
+          <t>356534; 404163</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1532,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1959,26 +1566,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>500</t>
         </is>
@@ -1993,22 +1580,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381620</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539760</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2027,26 +1614,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>353936</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>381620</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>539760</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>506968</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>353936</t>
         </is>
@@ -2061,62 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>354217; 405337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>513818; 564426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>480647; 534238</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>167640; 508272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>355794; 404449</t>
+          <t>354217; 405337</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>510537; 564878</t>
+          <t>513818; 564426</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>476194; 532948</t>
+          <t>480647; 534238</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155619; 503517</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>355794; 404449</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>510537; 564878</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>476194; 532948</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>155619; 503517</t>
+          <t>167640; 508272</t>
         </is>
       </c>
     </row>
@@ -2133,22 +1680,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2167,26 +1714,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>777</t>
         </is>
@@ -2201,22 +1728,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>595413</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>660096</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2235,26 +1762,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>568955</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>595413</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>660096</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>695903</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>568955</t>
         </is>
@@ -2269,62 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>565122; 629694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>626290; 691321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>666322; 725740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>530715; 634122</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>566070; 624292</t>
+          <t>565122; 629694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>629143; 691169</t>
+          <t>626290; 691321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>663512; 728004</t>
+          <t>666322; 725740</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>532307; 631797</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>566070; 624292</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>629143; 691169</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>663512; 728004</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>532307; 631797</t>
+          <t>530715; 634122</t>
         </is>
       </c>
     </row>
@@ -2341,22 +1828,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2375,26 +1862,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2420</t>
         </is>
@@ -2409,22 +1876,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2292976</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2242226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2443,26 +1910,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1571289</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2292976</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2242226</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1571289</t>
         </is>
@@ -2477,62 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1729293; 1845045</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2239652; 2357380</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2184223; 2299181</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1229447; 1725596</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1729293; 1845045</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2239652; 2357380</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2184223; 2299181</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1229447; 1725596</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
     </row>
@@ -2544,15 +1971,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P43C-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Habitat-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,43; 51,0</t>
+          <t>43,43; 51,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,42; 65,96</t>
+          <t>58,73; 65,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,22; 59,65</t>
+          <t>51,79; 59,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,1; 56,38</t>
+          <t>48,14; 55,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,43; 51,0</t>
+          <t>43,43; 51,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,42; 65,96</t>
+          <t>58,73; 65,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,22; 59,65</t>
+          <t>51,79; 59,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,1; 56,38</t>
+          <t>48,14; 55,31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 54,95</t>
+          <t>48,49; 55,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,7; 67,89</t>
+          <t>61,34; 67,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,25; 68,26</t>
+          <t>61,83; 67,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,94; 55,48</t>
+          <t>48,8; 55,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 54,95</t>
+          <t>48,49; 55,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,7; 67,89</t>
+          <t>61,34; 67,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,25; 68,26</t>
+          <t>61,83; 67,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,94; 55,48</t>
+          <t>48,8; 55,4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,53; 60,11</t>
+          <t>52,69; 60,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,92; 73,51</t>
+          <t>66,88; 73,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,56; 68,42</t>
+          <t>61,08; 68,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 70,15</t>
+          <t>60,87; 69,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,53; 60,11</t>
+          <t>52,69; 60,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,92; 73,51</t>
+          <t>66,88; 73,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,56; 68,42</t>
+          <t>61,08; 68,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 70,15</t>
+          <t>60,87; 69,18</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,31; 61,63</t>
+          <t>55,25; 61,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,23; 66,49</t>
+          <t>60,64; 66,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,46; 70,2</t>
+          <t>64,32; 70,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,57; 74,76</t>
+          <t>59,15; 65,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,31; 61,63</t>
+          <t>55,25; 61,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,23; 66,49</t>
+          <t>60,64; 66,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,46; 70,2</t>
+          <t>64,32; 70,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,57; 74,76</t>
+          <t>59,15; 65,37</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
     </row>
@@ -1332,42 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>292982; 344052</t>
+          <t>292949; 344812</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>403092; 455070</t>
+          <t>405174; 454472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>347554; 396955</t>
+          <t>344676; 396821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>248548; 285365</t>
+          <t>264132; 303457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>292982; 344052</t>
+          <t>292949; 344812</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>403092; 455070</t>
+          <t>405174; 454472</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>347554; 396955</t>
+          <t>344676; 396821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>248548; 285365</t>
+          <t>264132; 303457</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380965</t>
+          <t>423599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>380965</t>
+          <t>423599</t>
         </is>
       </c>
     </row>
@@ -1480,42 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>463808; 525577</t>
+          <t>463803; 527455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632346; 695696</t>
+          <t>628600; 690321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>639013; 700781</t>
+          <t>634732; 696045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>356534; 404163</t>
+          <t>397003; 450627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>463808; 525577</t>
+          <t>463803; 527455</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>632346; 695696</t>
+          <t>628600; 690321</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>639013; 700781</t>
+          <t>634732; 696045</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>356534; 404163</t>
+          <t>397003; 450627</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>354217; 405337</t>
+          <t>355290; 407470</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>513818; 564426</t>
+          <t>513537; 566599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>480647; 534238</t>
+          <t>476889; 532731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167640; 508272</t>
+          <t>344439; 391448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>354217; 405337</t>
+          <t>355290; 407470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>513818; 564426</t>
+          <t>513537; 566599</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>480647; 534238</t>
+          <t>476889; 532731</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>167640; 508272</t>
+          <t>344439; 391448</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531995</t>
         </is>
       </c>
     </row>
@@ -1776,42 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>565122; 629694</t>
+          <t>564533; 627819</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>626290; 691321</t>
+          <t>630564; 696516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>666322; 725740</t>
+          <t>664887; 727823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>530715; 634122</t>
+          <t>503919; 556917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>565122; 629694</t>
+          <t>564533; 627819</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>626290; 691321</t>
+          <t>630564; 696516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>666322; 725740</t>
+          <t>664887; 727823</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>530715; 634122</t>
+          <t>503919; 556917</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
     </row>
@@ -1924,42 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
     </row>
